--- a/single-summaries.xlsx
+++ b/single-summaries.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7930" yWindow="990" windowWidth="25160" windowHeight="18450" tabRatio="386" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4220" yWindow="990" windowWidth="25160" windowHeight="18450" tabRatio="386" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -256,6 +256,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="2" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -268,7 +269,6 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="2" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -621,24 +621,24 @@
   <dimension ref="A1:BA49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="13.36328125" customWidth="1" style="39" min="2" max="2"/>
-    <col width="8.453125" customWidth="1" style="39" min="3" max="3"/>
-    <col width="7.453125" customWidth="1" style="39" min="4" max="4"/>
+    <col width="13.36328125" customWidth="1" style="40" min="2" max="2"/>
+    <col width="8.453125" customWidth="1" style="40" min="3" max="3"/>
+    <col width="7.453125" customWidth="1" style="40" min="4" max="4"/>
     <col width="18.7265625" customWidth="1" style="18" min="5" max="5"/>
     <col width="11.54296875" customWidth="1" style="24" min="6" max="6"/>
     <col width="14.1796875" customWidth="1" style="24" min="7" max="7"/>
-    <col width="9" customWidth="1" style="39" min="8" max="8"/>
-    <col width="9.1796875" customWidth="1" style="39" min="9" max="11"/>
-    <col width="16.81640625" customWidth="1" style="39" min="12" max="19"/>
-    <col width="17.81640625" customWidth="1" style="39" min="20" max="20"/>
-    <col width="16.81640625" customWidth="1" style="39" min="21" max="23"/>
-    <col width="9.26953125" customWidth="1" style="39" min="24" max="28"/>
+    <col width="9" customWidth="1" style="40" min="8" max="8"/>
+    <col width="9.1796875" customWidth="1" style="40" min="9" max="11"/>
+    <col width="16.81640625" customWidth="1" style="40" min="12" max="19"/>
+    <col width="17.81640625" customWidth="1" style="40" min="20" max="20"/>
+    <col width="16.81640625" customWidth="1" style="40" min="21" max="23"/>
+    <col width="9.26953125" customWidth="1" style="40" min="24" max="28"/>
     <col width="9.26953125" customWidth="1" style="17" min="29" max="29"/>
-    <col width="9.26953125" customWidth="1" style="39" min="30" max="31"/>
+    <col width="9.26953125" customWidth="1" style="40" min="30" max="31"/>
     <col width="9.26953125" customWidth="1" style="18" min="32" max="32"/>
-    <col width="8.453125" customWidth="1" style="39" min="33" max="33"/>
-    <col width="6.453125" customWidth="1" style="39" min="34" max="41"/>
-    <col width="8" customWidth="1" style="39" min="42" max="42"/>
+    <col width="8.453125" customWidth="1" style="40" min="33" max="33"/>
+    <col width="6.453125" customWidth="1" style="40" min="34" max="41"/>
+    <col width="8" customWidth="1" style="40" min="42" max="42"/>
     <col width="25.7265625" customWidth="1" style="18" min="43" max="43"/>
     <col width="18.7265625" customWidth="1" style="18" min="44" max="44"/>
     <col width="13" customWidth="1" style="26" min="45" max="45"/>
@@ -649,12 +649,12 @@
     <col width="13.81640625" customWidth="1" style="26" min="50" max="50"/>
     <col width="18.7265625" customWidth="1" style="18" min="51" max="51"/>
     <col width="18.7265625" customWidth="1" style="42" min="52" max="52"/>
-    <col width="17.54296875" customWidth="1" style="39" min="53" max="53"/>
-    <col width="6.54296875" customWidth="1" style="39" min="54" max="56"/>
+    <col width="17.54296875" customWidth="1" style="40" min="53" max="53"/>
+    <col width="6.54296875" customWidth="1" style="40" min="54" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.5" customHeight="1" s="39">
-      <c r="T1" s="40" t="inlineStr">
+    <row r="1" ht="23.5" customHeight="1" s="40">
+      <c r="T1" s="41" t="inlineStr">
         <is>
           <t>CHU KỲ 10 KỲ</t>
         </is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="AF1" s="20" t="n"/>
-      <c r="AG1" s="38" t="inlineStr">
+      <c r="AG1" s="39" t="inlineStr">
         <is>
           <t>Trung bình/Kỳ</t>
         </is>
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>124.42</v>
+        <v>114.22</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>1661968600</v>
+        <v>967660930</v>
       </c>
       <c r="F3" t="n">
         <v>1951</v>
@@ -1005,19 +1005,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>23.08</v>
+        <v>30.77</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>76.92</v>
+        <v>53.85</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -1128,35 +1128,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR3" s="18" t="n">
-        <v>8468638600</v>
+        <v>7774330930</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>76.92</v>
+        <v>53.85</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>30.77</v>
+        <v>53.85</v>
       </c>
       <c r="AW3" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX3" s="18" t="n">
-        <v>8468638600</v>
+        <v>7774330930</v>
       </c>
       <c r="AY3" s="18" t="n">
-        <v>1661968600</v>
+        <v>967660930</v>
       </c>
       <c r="AZ3" t="n">
-        <v>124.42</v>
+        <v>114.22</v>
       </c>
       <c r="BA3">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v15.txt", "Click view")</f>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>147.35</v>
+        <v>164</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>3222983300</v>
+        <v>4356252612.5</v>
       </c>
       <c r="F4" t="n">
         <v>1962</v>
@@ -1191,19 +1191,19 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>23.08</v>
+        <v>53.85</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>76.92</v>
+        <v>46.15</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1215,11 +1215,11 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>23.08</v>
+        <v>30.77</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR4" s="18" t="n">
-        <v>10029653300</v>
+        <v>11162922612.5</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>76.92</v>
+        <v>46.15</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>38.46</v>
+        <v>46.15</v>
       </c>
       <c r="AW4" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX4" s="18" t="n">
-        <v>10029653300</v>
+        <v>11162922612.5</v>
       </c>
       <c r="AY4" s="18" t="n">
-        <v>3222983300</v>
+        <v>4356252612.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>147.35</v>
+        <v>164</v>
       </c>
       <c r="BA4">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v46.txt", "Click view")</f>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>133.06</v>
+        <v>144.82</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>2250584700</v>
+        <v>3050679824.700001</v>
       </c>
       <c r="F5" t="n">
         <v>1962</v>
@@ -1377,51 +1377,51 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>61.54</v>
+        <v>69.23</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>38.46</v>
+        <v>30.77</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>30.77</v>
+        <v>23.08</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1500,15 +1500,15 @@
         <v>6806670000</v>
       </c>
       <c r="AR5" s="18" t="n">
-        <v>9057254700</v>
+        <v>9857349824.700001</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>38.46</v>
+        <v>30.77</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1522,13 +1522,13 @@
         <v>6806670000</v>
       </c>
       <c r="AX5" s="18" t="n">
-        <v>9057254700</v>
+        <v>9857349824.700001</v>
       </c>
       <c r="AY5" s="18" t="n">
-        <v>2250584700</v>
+        <v>3050679824.700001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>133.06</v>
+        <v>144.82</v>
       </c>
       <c r="BA5">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v80.txt", "Click view")</f>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>140.22</v>
+        <v>130.92</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>2737355000</v>
+        <v>2104887837.5</v>
       </c>
       <c r="F6" t="n">
         <v>1962</v>
@@ -1563,19 +1563,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>23.08</v>
+        <v>53.85</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>76.92</v>
+        <v>46.15</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1587,11 +1587,11 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>23.08</v>
+        <v>30.77</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1686,35 +1686,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR6" s="18" t="n">
-        <v>9544025000</v>
+        <v>8911557837.5</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>76.92</v>
+        <v>46.15</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>38.46</v>
+        <v>46.15</v>
       </c>
       <c r="AW6" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX6" s="18" t="n">
-        <v>9544025000</v>
+        <v>8911557837.5</v>
       </c>
       <c r="AY6" s="18" t="n">
-        <v>2737355000</v>
+        <v>2104887837.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>140.22</v>
+        <v>130.92</v>
       </c>
       <c r="BA6">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v81.txt", "Click view")</f>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>136.52</v>
+        <v>153.76</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>2485722000</v>
+        <v>3659193824.700001</v>
       </c>
       <c r="F7" t="n">
         <v>1962</v>
@@ -1749,27 +1749,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30.77</v>
+        <v>38.46</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>61.54</v>
+        <v>53.85</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>30.77</v>
+        <v>23.08</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1789,11 +1789,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1872,35 +1872,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR7" s="18" t="n">
-        <v>9292392000</v>
+        <v>10465863824.7</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>61.54</v>
+        <v>53.85</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="AV7" t="n">
-        <v>38.46</v>
+        <v>53.85</v>
       </c>
       <c r="AW7" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX7" s="18" t="n">
-        <v>9292392000</v>
+        <v>10465863824.7</v>
       </c>
       <c r="AY7" s="18" t="n">
-        <v>2485722000</v>
+        <v>3659193824.700001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>136.52</v>
+        <v>153.76</v>
       </c>
       <c r="BA7">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v82.txt", "Click view")</f>
@@ -1908,7 +1908,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="35" t="n">
         <v>83</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>134.59</v>
+        <v>114.7</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>2354719900</v>
+        <v>1000670717.8</v>
       </c>
       <c r="F8" t="n">
         <v>1951</v>
@@ -1935,19 +1935,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/13</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="J8" s="41" t="inlineStr">
-        <is>
-          <t>12/13</t>
-        </is>
-      </c>
-      <c r="K8" s="41" t="n">
-        <v>92.31</v>
+        <v>38.46</v>
+      </c>
+      <c r="J8" s="35" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="K8" s="35" t="n">
+        <v>61.54</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1959,11 +1959,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>15.38</v>
+        <v>23.08</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -2058,35 +2058,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR8" s="18" t="n">
-        <v>9161389900</v>
-      </c>
-      <c r="AS8" s="41" t="inlineStr">
-        <is>
-          <t>12/13</t>
-        </is>
-      </c>
-      <c r="AT8" s="41" t="n">
-        <v>92.31</v>
+        <v>7807340717.8</v>
+      </c>
+      <c r="AS8" s="35" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="AT8" s="35" t="n">
+        <v>61.54</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>53.85</v>
+        <v>61.54</v>
       </c>
       <c r="AW8" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX8" s="18" t="n">
-        <v>9161389900</v>
+        <v>7807340717.8</v>
       </c>
       <c r="AY8" s="18" t="n">
-        <v>2354719900</v>
-      </c>
-      <c r="AZ8" s="41" t="n">
-        <v>134.59</v>
+        <v>1000670717.8</v>
+      </c>
+      <c r="AZ8" s="35" t="n">
+        <v>114.7</v>
       </c>
       <c r="BA8">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v83.txt", "Click view")</f>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>125.01</v>
+        <v>104.69</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>1702054600</v>
+        <v>319306217.8000002</v>
       </c>
       <c r="F9" t="n">
         <v>1951</v>
@@ -2121,19 +2121,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>30.77</v>
+        <v>46.15</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>69.23</v>
+        <v>53.85</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2145,19 +2145,19 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2244,35 +2244,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR9" s="18" t="n">
-        <v>8508724600</v>
+        <v>7125976217.8</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>69.23</v>
+        <v>53.85</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>30.77</v>
+        <v>53.85</v>
       </c>
       <c r="AW9" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX9" s="18" t="n">
-        <v>8508724600</v>
+        <v>7125976217.8</v>
       </c>
       <c r="AY9" s="18" t="n">
-        <v>1702054600</v>
+        <v>319306217.8000002</v>
       </c>
       <c r="AZ9" t="n">
-        <v>125.01</v>
+        <v>104.69</v>
       </c>
       <c r="BA9">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v84.txt", "Click view")</f>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>136.98</v>
+        <v>116</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>2517277100</v>
+        <v>1088868717.8</v>
       </c>
       <c r="F10" t="n">
         <v>1951</v>
@@ -2307,27 +2307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>30.77</v>
+        <v>46.15</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>69.23</v>
+        <v>46.15</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>53.85</v>
+        <v>38.46</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2347,11 +2347,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>15.38</v>
+        <v>23.08</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2430,35 +2430,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR10" s="18" t="n">
-        <v>9323947100</v>
+        <v>7895538717.8</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>69.23</v>
+        <v>46.15</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
       <c r="AV10" t="n">
-        <v>53.85</v>
+        <v>46.15</v>
       </c>
       <c r="AW10" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX10" s="18" t="n">
-        <v>9323947100</v>
+        <v>7895538717.8</v>
       </c>
       <c r="AY10" s="18" t="n">
-        <v>2517277100</v>
+        <v>1088868717.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>136.98</v>
+        <v>116</v>
       </c>
       <c r="BA10">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v85.txt", "Click view")</f>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>132.88</v>
+        <v>105.01</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>2238022300</v>
+        <v>340824767.8000002</v>
       </c>
       <c r="F11" t="n">
         <v>1964</v>
@@ -2493,43 +2493,43 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/13</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>23.08</v>
+        <v>38.46</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>76.92</v>
+        <v>53.85</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>46.15</v>
+        <v>30.77</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>23.08</v>
+        <v>30.77</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>15.38</v>
+        <v>30.77</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2616,35 +2616,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR11" s="18" t="n">
-        <v>9044692300</v>
+        <v>7147494767.8</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>76.92</v>
+        <v>53.85</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="AV11" t="n">
-        <v>46.15</v>
+        <v>53.85</v>
       </c>
       <c r="AW11" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX11" s="18" t="n">
-        <v>9044692300</v>
+        <v>7147494767.8</v>
       </c>
       <c r="AY11" s="18" t="n">
-        <v>2238022300</v>
+        <v>340824767.8000002</v>
       </c>
       <c r="AZ11" t="n">
-        <v>132.88</v>
+        <v>105.01</v>
       </c>
       <c r="BA11">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v86.txt", "Click view")</f>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>127.08</v>
+        <v>93.45</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>1843505100</v>
+        <v>-445558020</v>
       </c>
       <c r="F12" t="n">
         <v>1964</v>
@@ -2679,27 +2679,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>6/13</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>5/13</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>38.46</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>7/13</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>53.85</v>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>30.77</v>
+        <v>23.08</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2711,19 +2711,19 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>15.38</v>
+        <v>7.69</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>15.38</v>
+        <v>7.69</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2802,35 +2802,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR12" s="18" t="n">
-        <v>8650175100</v>
+        <v>6361111980</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>53.85</v>
+        <v>38.46</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
       <c r="AV12" t="n">
-        <v>30.77</v>
+        <v>38.46</v>
       </c>
       <c r="AW12" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX12" s="18" t="n">
-        <v>8650175100</v>
+        <v>6361111980</v>
       </c>
       <c r="AY12" s="18" t="n">
-        <v>1843505100</v>
+        <v>-445558020</v>
       </c>
       <c r="AZ12" t="n">
-        <v>127.08</v>
+        <v>93.45</v>
       </c>
       <c r="BA12">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v87.txt", "Click view")</f>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>132.67</v>
+        <v>108.64</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>2223432200</v>
+        <v>588391055.6000004</v>
       </c>
       <c r="F13" t="n">
         <v>1964</v>
@@ -2865,51 +2865,51 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>46.15</v>
+        <v>53.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>53.85</v>
+        <v>38.46</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>46.15</v>
+        <v>30.77</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>23.08</v>
+        <v>30.77</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>23.08</v>
+        <v>30.77</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2988,35 +2988,35 @@
         <v>6806670000</v>
       </c>
       <c r="AR13" s="18" t="n">
-        <v>9030102200</v>
+        <v>7395061055.6</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>53.85</v>
+        <v>38.46</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
       <c r="AV13" t="n">
-        <v>53.85</v>
+        <v>38.46</v>
       </c>
       <c r="AW13" s="18" t="n">
         <v>6806670000</v>
       </c>
       <c r="AX13" s="18" t="n">
-        <v>9030102200</v>
+        <v>7395061055.6</v>
       </c>
       <c r="AY13" s="18" t="n">
-        <v>2223432200</v>
+        <v>588391055.6000004</v>
       </c>
       <c r="AZ13" t="n">
-        <v>132.67</v>
+        <v>108.64</v>
       </c>
       <c r="BA13">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v88.txt", "Click view")</f>
@@ -3024,40 +3024,607 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n"/>
+      <c r="A14" s="18" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n"/>
+      <c r="A15" s="18" t="n">
+        <v>89</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>38,54,70,96,146,168,192,266,290,340,392,430,462</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>142.09</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2865123767.799999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G15" t="n">
+        <v>179</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>100</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>100</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1672</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>169</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1841</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>134</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>128.62</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>126.23</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6806670000</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9671793767.799999</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+      <c r="AV15" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>6806670000</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9671793767.799999</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>2865123767.799999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>142.09</v>
+      </c>
+      <c r="BA15">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v89.txt", "Click view")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n"/>
+      <c r="A16" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>38,54,70,96,146,168,192,266,290,340,392,430,462</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>135.88</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2441951410</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G16" t="n">
+        <v>154</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>100</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>100</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1703</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>138</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1841</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>99</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>134</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>131</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>128.15</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>6806670000</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9248621410</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+      <c r="AV16" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6806670000</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9248621410</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>2441951410</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>135.88</v>
+      </c>
+      <c r="BA16">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v90.txt", "Click view")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n"/>
+      <c r="A17" s="18" t="n">
+        <v>91</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>38,54,70,96,146,168,192,266,290,340,392,430,462</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>121.92</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1491952960</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G17" t="n">
+        <v>145</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>100</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>100</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1703</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>138</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1841</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>107</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>134</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>131</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>128.85</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6806670000</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8298622960</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+      <c r="AV17" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6806670000</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>8298622960</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1491952960</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>121.92</v>
+      </c>
+      <c r="BA17">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v91.txt", "Click view")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n"/>
+      <c r="A18" s="18" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n"/>
+      <c r="A19" s="18" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n"/>
+      <c r="A20" s="18" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n"/>
+      <c r="A21" s="18" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n"/>
+      <c r="A22" s="18" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n"/>
+      <c r="A23" s="18" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n"/>
+      <c r="A24" s="18" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n"/>
+      <c r="A25" s="18" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="n"/>
